--- a/光伏配储项目/电价数据/2026/良骏站.xlsx
+++ b/光伏配储项目/电价数据/2026/良骏站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5101600000000001</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38637</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.74224</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5709500000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.57656</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.50059</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.49647</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43756</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45438</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43989</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42317</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41987</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4088</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40206</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42309</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41254</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41693</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42066</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42389</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44398</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.28271</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.11483</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09359000000000001</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.10122</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.08695</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.11075</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.0458</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.09122</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.11269</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.11781</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.10791</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08974</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.09403</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.06106</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.01063</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15041</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21578</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.24979</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.28609</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.20763</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.08971</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.00311</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.13767</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.26642</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.2881</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.1841</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.29424</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.54147</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.40173</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.47969</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.90695</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.58762</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43725</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44324</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42376</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.56624</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.44482</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.5962999999999999</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.79544</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.63542</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.61095</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.7237</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.8377899999999999</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41889</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.65901</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.61673</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.6644800000000001</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.6038300000000001</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.59854</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6330399999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.60301</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.46677</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48758</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.3997</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41616</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42582</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6866599999999999</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.71548</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.77298</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.21083</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.83612</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.52686</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51928</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5053799999999999</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50732</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49018</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40034</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47037</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39138</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37534</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.3752799999999999</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38022</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41958</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.50132</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59749</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.6890499999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.4304</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.41356</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.40833</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5040899999999999</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.15405</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29926</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.04057</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.48011</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7776900000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.93168</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.7800499999999999</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.48685</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.10645</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28195</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.46789</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.26197</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.25277</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.26356</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.46844</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.41233</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29164</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.38395</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.54483</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.67039</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.51862</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.6859500000000001</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7536</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.75934</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.5258400000000001</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.50298</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.81743</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.49691</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.41324</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.93084</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.46025</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.6076</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44225</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43583</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33459</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.53201</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.37253</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.40563</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38293</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40383</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.40755</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3901</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36656</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43589</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45236</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39617</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37175</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36672</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38459</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47387</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45219</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44648</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.41429</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.19598</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.42961</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26682</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.46502</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.39754</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.49996</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.47228</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.38946</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.14595</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.29831</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.25054</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.2996</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.28082</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.27703</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29338</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.28134</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.38211</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.42278</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.39975</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.44908</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.41156</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.45047</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.5560700000000001</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.36376</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.37758</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.50996</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.59533</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.52352</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.5885499999999999</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.44905</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.41207</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.46527</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.44396</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.43118</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.45181</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.43795</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.38675</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.41117</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.39153</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39499</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.3619</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.40838</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46057</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30846</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38948</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.30173</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.27348</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.30219</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.13167</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.20183</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.15885</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.23592</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.5025299999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.42297</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.06468</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.05821</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.12911</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.30153</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.28329</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.15885</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.17338</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.50145</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.05305</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.12073</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.21028</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.23158</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.3856</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.2262</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.24419</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.21324</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.27164</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14338</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.2627</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.27813</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.30194</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.41868</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.5694900000000001</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.45363</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.43895</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.36571</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31591</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29564</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31186</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29826</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29711</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29969</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37817</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38249</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35634</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29279</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30583</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29289</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29022</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29214</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30667</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27931</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26047</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.05021</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.0454</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.05154</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04417</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.0471</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.05006</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04758</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03581</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04754</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04639</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04275</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04166</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.0417</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04228</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04199</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04068</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04291</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.0461</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04331</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04239</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.043</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04376</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04672</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04355</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04713000000000001</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.2191</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04708</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05277</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05558</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.04922</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00128</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.15688</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.05037</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.10903</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29332</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29367</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38581</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.3919</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38724</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.38973</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.41379</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39972</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.43338</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4676</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39649</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41728</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35532</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35106</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.67536</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44653</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42363</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42369</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04332</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04685</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04566</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04604</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04604</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04604</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04371</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03697</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04292</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10491</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00104</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04109</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04359</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.0436</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04536</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04536</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04337</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04299</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04521</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04301</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04209</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04513</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04502</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04517</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04327</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04396</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04397</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.0445</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04989</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04725</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04758</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20027</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14308</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30507</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30035</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29544</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29326</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29394</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29292</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29123</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29539</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26924</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29848</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30883</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33586</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31823</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4050299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30176</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.2815299999999999</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29496</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29118</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28843</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28132</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27154</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27134</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28142</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17266</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15891</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17126</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14798</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15971</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15889</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23663</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21431</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22685</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26933</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28613</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29115</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29118</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28132</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28142</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.2809</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27086</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28129</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29457</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38295</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.4275</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45374</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41748</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41429</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.3892</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29924</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15665</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29309</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38522</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076499999999999</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79099</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62202</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49795</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92035</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49453</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91696</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8714700000000001</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.30084</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.89589</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63305</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19534</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87283</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5483</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.3393</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03872</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53925</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79816</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53066</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7802</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78326</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87766</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87763</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49989</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40526</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40861</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45767</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21572</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8791599999999999</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55122</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63049</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5405</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.5002099999999999</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45692</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42531</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43871</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45039</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39039</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45284</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42034</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36533</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41491</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43393</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.3905</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40507</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45091</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40028</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5870700000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42806</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59621</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60229</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6672400000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46695</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41722</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5787599999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45076</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.87676</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63315</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.86275</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.84473</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86114</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44054</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30543</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.45972</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.29147</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41029</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45273</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41529</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39176</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.3752200000000001</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35349</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9298</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46896</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.4311</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.4895</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38453</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41006</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40039</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50048</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38788</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36317</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29068</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28978</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.2829</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.1652</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30063</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30276</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29717</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26202</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19937</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27729</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.20355</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27744</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30472</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29344</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31317</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29003</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25562</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.28978</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27631</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43538</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.30549</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42322</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44843</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42064</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40194</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40067</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59742</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89032</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.30753</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.11674</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6889500000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7758200000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.63955</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5730599999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44632</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44612</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49428</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43569</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43346</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41165</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40959</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.41996</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49465</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40959</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43006</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41011</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42944</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38782</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42443</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44612</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39353</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41982</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43033</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40959</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.40957</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39753</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.37559</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.39804</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49485</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29664</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36466</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3092200000000001</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30649</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30301</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.17799</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5689299999999999</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.37209</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.2503</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.08856</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.56825</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.29985</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.29231</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.26375</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.39268</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26235</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25674</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30597</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30694</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29316</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.39896</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39749</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37036</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.36522</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36247</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.37261</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5755</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.45944</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7502000000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46002</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.4376</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42279</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38613</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36911</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32433</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42023</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.3098399999999999</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38875</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39787</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37341</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28124</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.07284</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29347</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23826</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.15267</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.15686</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29032</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.16409</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14901</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14858</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14889</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14929</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.27446</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.15441</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.28352</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26911</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.15302</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.15129</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11977</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10917</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.15342</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14755</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.15224</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28952</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.30572</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36894</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.3774</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39543</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38291</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44636</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39808</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.38902</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39575</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44054</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43636</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4357</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44046</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44044</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.4002</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39585</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38987</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34909</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.53267</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38646</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46328</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.41987</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41219</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37777</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37746</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.3901</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37811</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.38862</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.3683999999999999</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37814</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36842</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36302</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29726</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3156600000000001</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28152</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26737</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.2631</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.1967</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30566</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24778</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24004</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2671</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28506</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29975</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29173</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28149</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30253</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28282</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.38168</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.39538</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.25296</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.4182</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36639</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37436</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38391</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35931</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.37068</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.44007</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37026</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38703</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31309</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.30172</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39146</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.40258</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.45322</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.44771</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30324</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.28381</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25028</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.28361</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.10334</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.21904</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25352</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.29632</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.2776</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30179</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29284</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.4158</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.38648</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.47664</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.71135</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33435</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.26766</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30445</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30428</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.3048</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28874</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.3252</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32383</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28438</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37747</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36878</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37408</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39703</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38717</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40169</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.39319</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3828</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34962</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.35281</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35797</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.36297</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38128</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38459</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4395</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40974</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.39317</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37843</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6906</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.77378</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47956</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45611</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39261</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.36814</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.35076</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41857</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37742</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36217</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.3915</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38251</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.36549</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26538</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14729</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30165</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.2853</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28412</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19917</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25763</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28009</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28001</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21824</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26187</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28498</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.2782</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28989</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29136</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30534</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14987</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29287</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43378</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38398</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.4223</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6029800000000001</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.66334</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.69157</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.48811</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.7397100000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.5304</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.89022</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.47054</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48284</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40776</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.38253</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36188</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48354</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43051</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.43195</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37479</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36724</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36009</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49107</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.56116</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.50298</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.5056</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42251</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40443</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40854</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40965</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41934</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.3989</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39887</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41485</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40562</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39266</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38549</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.4153</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41911</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38786</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.4019</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41427</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40388</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44581</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45675</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56055</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49403</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.5904400000000001</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.46526</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44323</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.39024</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.38762</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42155</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.42691</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.52323</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.46318</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29796</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36583</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.38386</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40243</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28863</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.36709</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6410800000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.36602</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.15693</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.28183</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35314</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.40987</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43329</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48706</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43483</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.5075500000000001</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.5432899999999999</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.61382</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.78973</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.8073400000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.89403</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.7037</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.8047000000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.60327</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5573400000000001</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.93688</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.8591</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6313</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.71033</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.45486</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47232</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.50891</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47802</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.4956</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41815</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.56712</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42884</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44347</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.46981</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45657</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.43338</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.45732</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.43374</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39818</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40722</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.41006</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38692</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37623</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37111</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36398</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.39627</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39014</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38792</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.38792</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40821</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36931</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39515</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39648</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.40495</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.39464</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36885</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.18238</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40516</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44659</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46397</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11052</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.1808</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29989</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29496</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37223</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.3789</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37357</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38607</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41601</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42836</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41277</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41252</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38204</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37614</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38478</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.4085299999999999</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37283</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37677</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.4103</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38784</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.40181</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38023</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36417</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39536</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38046</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36552</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44481</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.3935</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39331</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37893</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30533</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27173</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22798</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28836</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23061</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28834</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25032</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25312</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13974</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29271</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29923</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24954</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25144</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28725</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16922</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18098</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27236</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22809</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24862</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26214</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23233</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27552</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28429</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28326</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37318</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35796</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36923</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36443</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36883</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35047</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31392</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30879</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30566</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29047</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.25974</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.24692</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16934</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.20881</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.21204</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01788</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00037</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.02843</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.10818</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.0155</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03964</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.02109</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04148</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04873</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.0484</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02673</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03126</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04967</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.12663</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04953</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28887</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04971</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0495</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03345</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04307</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.17076</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.19946</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.23808</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.26615</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.26777</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.26645</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.27165</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.28666</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28182</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29135</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.29331</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28638</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.28479</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29521</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.14643</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5798</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.17177</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.29571</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.26598</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30832</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.2892</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.27682</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.25324</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.24343</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.26924</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.25931</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.22703</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.25389</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.25121</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.27385</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.27697</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.2558</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.30218</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.27893</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.36877</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.31109</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.28105</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.2814</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.23343</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.16907</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6454800000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.6450399999999999</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.66296</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.58333</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.16715</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.30618</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09273999999999999</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.23997</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.1817</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.12803</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.13507</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.0912</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.22988</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.11752</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.04219</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.05434000000000001</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.10737</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.17952</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02548</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.12678</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.13243</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.15277</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.01484</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.11007</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.11671</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.11778</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.14894</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.2543</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29283</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27445</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.40139</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36934</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35333</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.3237</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.05062</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.48681</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.56028</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.3777</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.42105</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41126</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.43052</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.47019</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.38963</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.46485</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.38711</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.3767799999999999</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.44268</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.13988</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27475</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27009</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.27527</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29154</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32373</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.45916</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.42159</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35633</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33385</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.3736</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.28483</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.38996</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.63303</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.60422</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.53661</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37344</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36953</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.30835</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26084</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.28128</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28364</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41568</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39787</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.51106</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.52565</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.45745</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.47066</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.41394</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.46451</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.38093</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40996</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.4227</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.37452</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37466</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.38601</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38464</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.38886</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41708</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.4505</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.40218</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.38431</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.48513</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.41596</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.39153</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.41638</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37975</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37265</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.5543400000000001</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.37657</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47855</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37414</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37855</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36893</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36677</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36401</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37727</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.41166</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.38294</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36999</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.39104</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.40986</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.37488</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43563</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.29118</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36619</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.26664</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29395</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38281</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37466</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38395</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38974</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.47084</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.39768</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.45103</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42921</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42957</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.51762</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.6031599999999999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.6018300000000001</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.39364</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45484</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.58145</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.51875</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5685</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.5273300000000001</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.40299</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.57062</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.50343</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.05685</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.90604</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.6167</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.6091599999999999</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.41027</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.4649</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.41251</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.38197</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.3776</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37418</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.38085</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.26817</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37043</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30478</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.29528</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31181</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.23962</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.26902</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.2881</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.13246</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.2236</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.1757</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.05834</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.14549</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.02691</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.19575</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.16294</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.00135</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.29694</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25679</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.15501</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05364</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.0499</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.06388000000000001</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.14888</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.07142</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05372</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.16949</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.14051</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.1635</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.2642</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.2985</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.28236</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36655</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36277</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.2577</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.30781</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.39253</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.41109</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38299</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.41468</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41853</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38881</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39329</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42725</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39535</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.39491</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.43047</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38786</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.45014</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.39897</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.39102</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37379</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.56448</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38087</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.9824400000000001</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.3679</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.48355</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.4284</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38392</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38242</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37704</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38026</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.3863</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38296</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.27114</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.26486</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.27805</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.26534</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11378</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01807</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01828</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.0176</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.04116</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.17133</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.0406</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00563</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01833</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04597</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01557</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.01534</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01545</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.16323</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.26508</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04489</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.24164</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.15994</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.25496</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.28821</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.31591</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.48312</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41588</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40622</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38952</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5698799999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.62821</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38612</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.3972</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.37307</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.4051</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.40191</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42841</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.38534</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39766</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36885</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.37363</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36677</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36301</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3752200000000001</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.6137699999999999</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38638</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3883</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36407</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.44339</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39266</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35723</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28315</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.26016</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.23378</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14588</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2346</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.23754</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11583</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15329</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.04015999999999999</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.01639</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04697</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04761</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04649</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04681</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04475</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.0418</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.08001999999999999</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02904</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06434000000000001</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09856000000000001</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.17393</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.19844</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12246</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.26376</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.23274</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12557</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04803</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.2653</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.14931</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.11849</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.23876</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.18965</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.24462</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.24868</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.20759</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.24951</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.28042</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.28199</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.30497</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38709</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37139</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.38713</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38855</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40103</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41242</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.51485</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40137</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41362</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.41363</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.4049700000000001</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38216</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.39368</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.41155</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38318</v>
       </c>
     </row>
   </sheetData>
